--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Rural Opportunities Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Rural Opportunities Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558B09D7-91E2-4345-9BF4-EC4E9602B1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221EEAAF-09CE-4579-9D28-E56123B937AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="134">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Rural Opportunities Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -58,7 +58,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments</t>
+    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
   </si>
   <si>
     <t/>
@@ -67,6 +67,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>Bharti Airtel Ltd.</t>
   </si>
   <si>
@@ -85,13 +94,28 @@
     <t>Banks</t>
   </si>
   <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
   </si>
   <si>
     <t>Bank Of Baroda</t>
@@ -100,10 +124,19 @@
     <t>INE028A01039</t>
   </si>
   <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
   </si>
   <si>
     <t>SBI Life Insurance Company Ltd.</t>
@@ -124,40 +157,154 @@
     <t>Finance</t>
   </si>
   <si>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE0J1Y01017</t>
+  </si>
+  <si>
     <t>Max Financial Services Ltd.</t>
   </si>
   <si>
     <t>INE180A01020</t>
   </si>
   <si>
+    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE335Y01020</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
     <t>HDFC Life Insurance Company Ltd.</t>
   </si>
   <si>
     <t>INE795G01014</t>
   </si>
   <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Birla Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE340A01012</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>JK Lakshmi Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE786A01032</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Dalmia Bharat Ltd.</t>
+  </si>
+  <si>
+    <t>INE00R701025</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Gujarat State Fertilizers and Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE026A01025</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
     <t>Ambuja Cements Ltd.</t>
   </si>
   <si>
     <t>INE079A01024</t>
   </si>
   <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Life Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE0J1Y01017</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
+    <t>Crompton Greaves Consumer Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE299U01018</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Emami Ltd.</t>
+  </si>
+  <si>
+    <t>INE548C01032</t>
+  </si>
+  <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
+  </si>
+  <si>
+    <t>Bayer Cropscience Ltd.</t>
+  </si>
+  <si>
+    <t>INE462A01022</t>
   </si>
   <si>
     <t>Tata Motors Ltd.</t>
@@ -166,118 +313,7 @@
     <t>INE155A01022</t>
   </si>
   <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
-  </si>
-  <si>
-    <t>Havells India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176B01034</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE823G01014</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Gujarat State Fertilizers and Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE026A01025</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Birla Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE340A01012</t>
+    <t>Bharti Airtel Ltd. $$</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -313,6 +349,21 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>91 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z164</t>
+  </si>
+  <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
@@ -334,16 +385,31 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of Stock Future / Index Future</t>
+  </si>
+  <si>
+    <t>Stock / Index Futures</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda $$</t>
+  </si>
+  <si>
+    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>$$ - Derivatives.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -355,7 +421,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - Nifty Rural TRI</t>
+    <t>Benchmark Name - CRISIL-IBX AAA Financial Services Index – Dec 2026</t>
   </si>
 </sst>
 </file>
@@ -371,7 +437,7 @@
     <numFmt numFmtId="165" formatCode="##0.00%"/>
     <numFmt numFmtId="166" formatCode="##0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -424,12 +490,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -562,9 +622,8 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -577,13 +636,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -632,7 +692,6 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
@@ -661,13 +720,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -691,7 +750,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16078200"/>
+          <a:off x="666750" y="19697700"/>
           <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -708,13 +767,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -738,7 +797,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18935700"/>
+          <a:off x="666750" y="22555200"/>
           <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1074,14 +1133,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="55.28515625" style="24" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="16.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="9.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="28.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="36" style="24" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="10.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="38.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="8" max="8" width="11.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1090,43 +1149,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
@@ -1174,10 +1233,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>40241.019999999997</v>
+        <v>116165.52</v>
       </c>
       <c r="H5" s="13">
-        <v>0.32642813275280003</v>
+        <v>0.84705175660230003</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1211,10 +1270,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>40241.019999999997</v>
+        <v>116165.52</v>
       </c>
       <c r="H7" s="13">
-        <v>0.32642813275280003</v>
+        <v>0.84705175660230003</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1237,13 +1296,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>368996</v>
+        <v>523806</v>
       </c>
       <c r="G8" s="18">
-        <v>6000.98</v>
+        <v>12300.54</v>
       </c>
       <c r="H8" s="19">
-        <v>4.8678902674300001E-2</v>
+        <v>8.9692655911800007E-2</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1266,13 +1325,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="17">
-        <v>563539</v>
+        <v>484067</v>
       </c>
       <c r="G9" s="18">
-        <v>4355.59</v>
+        <v>8985.25</v>
       </c>
       <c r="H9" s="19">
-        <v>3.5331786091400003E-2</v>
+        <v>6.5518337937299997E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1295,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="17">
-        <v>151000</v>
+        <v>1021039</v>
       </c>
       <c r="G10" s="18">
-        <v>3727.89</v>
+        <v>8293.9</v>
       </c>
       <c r="H10" s="19">
-        <v>3.0239993216199999E-2</v>
+        <v>6.0477175706600002E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1321,16 +1380,16 @@
         <v>13</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" s="17">
-        <v>1620000</v>
+        <v>1908996</v>
       </c>
       <c r="G11" s="18">
-        <v>3456.92</v>
+        <v>7980.56</v>
       </c>
       <c r="H11" s="19">
-        <v>2.8041931856599998E-2</v>
+        <v>5.8192373835900001E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1350,16 +1409,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>555000</v>
+        <v>1953560</v>
       </c>
       <c r="G12" s="18">
-        <v>2483.63</v>
+        <v>6522.94</v>
       </c>
       <c r="H12" s="19">
-        <v>2.01467732018E-2</v>
+        <v>4.7563750286800002E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1370,25 +1429,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>162765</v>
+        <v>208408</v>
       </c>
       <c r="G13" s="18">
-        <v>2414.7800000000002</v>
+        <v>6203.89</v>
       </c>
       <c r="H13" s="19">
-        <v>1.95882740152E-2</v>
+        <v>4.5237312433799998E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1399,25 +1458,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F14" s="17">
-        <v>246000</v>
+        <v>2304099</v>
       </c>
       <c r="G14" s="18">
-        <v>1471.33</v>
+        <v>5749.88</v>
       </c>
       <c r="H14" s="19">
-        <v>1.1935172233799999E-2</v>
+        <v>4.1926777879200003E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1437,16 +1496,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F15" s="17">
-        <v>123503</v>
+        <v>226713</v>
       </c>
       <c r="G15" s="18">
-        <v>1377.98</v>
+        <v>5432.5</v>
       </c>
       <c r="H15" s="19">
-        <v>1.1177933322000001E-2</v>
+        <v>3.9612517274899998E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1457,25 +1516,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" s="17">
-        <v>193000</v>
+        <v>187781</v>
       </c>
       <c r="G16" s="18">
-        <v>1231.44</v>
+        <v>5221.8100000000004</v>
       </c>
       <c r="H16" s="19">
-        <v>9.9892264111999998E-3</v>
+        <v>3.8076215155299999E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1486,25 +1545,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="17">
-        <v>238310</v>
+        <v>265890</v>
       </c>
       <c r="G17" s="18">
-        <v>1222.05</v>
+        <v>4818.46</v>
       </c>
       <c r="H17" s="19">
-        <v>9.9130563695999999E-3</v>
+        <v>3.5135081452100002E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1515,25 +1574,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F18" s="17">
-        <v>144374</v>
+        <v>681000</v>
       </c>
       <c r="G18" s="18">
-        <v>1220.6099999999999</v>
+        <v>4061.82</v>
       </c>
       <c r="H18" s="19">
-        <v>9.9013753408999997E-3</v>
+        <v>2.96178398375E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1544,25 +1603,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F19" s="17">
-        <v>370000</v>
+        <v>379374</v>
       </c>
       <c r="G19" s="18">
-        <v>1198.8</v>
+        <v>3620.94</v>
       </c>
       <c r="H19" s="19">
-        <v>9.7244564263999998E-3</v>
+        <v>2.64030461668E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1573,25 +1632,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F20" s="17">
-        <v>160000</v>
+        <v>220503</v>
       </c>
       <c r="G20" s="18">
-        <v>1145.76</v>
+        <v>3313.5</v>
       </c>
       <c r="H20" s="19">
-        <v>9.2942052010999993E-3</v>
+        <v>2.4161265713799999E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1611,16 +1670,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F21" s="17">
-        <v>60559</v>
+        <v>402805</v>
       </c>
       <c r="G21" s="18">
-        <v>1130.24</v>
+        <v>3045.21</v>
       </c>
       <c r="H21" s="19">
-        <v>9.1683096691000006E-3</v>
+        <v>2.22049578887E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1631,25 +1690,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F22" s="17">
-        <v>32291</v>
+        <v>33495</v>
       </c>
       <c r="G22" s="18">
-        <v>965.45</v>
+        <v>2882.91</v>
       </c>
       <c r="H22" s="19">
-        <v>7.8315619427000004E-3</v>
+        <v>2.1021504312300002E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1660,25 +1719,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F23" s="17">
-        <v>35799</v>
+        <v>350281</v>
       </c>
       <c r="G23" s="18">
-        <v>828.1</v>
+        <v>2721.16</v>
       </c>
       <c r="H23" s="19">
-        <v>6.7174027083000002E-3</v>
+        <v>1.9842061207100001E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1698,16 +1757,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F24" s="17">
-        <v>15000</v>
+        <v>49083</v>
       </c>
       <c r="G24" s="18">
-        <v>650.87</v>
+        <v>2704.72</v>
       </c>
       <c r="H24" s="19">
-        <v>5.2797438724000003E-3</v>
+        <v>1.9722184578700001E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1727,16 +1786,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F25" s="17">
-        <v>25000</v>
+        <v>21562</v>
       </c>
       <c r="G25" s="18">
-        <v>627.21</v>
+        <v>2656.22</v>
       </c>
       <c r="H25" s="19">
-        <v>5.0878180806999997E-3</v>
+        <v>1.93685339412E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1756,16 +1815,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F26" s="17">
-        <v>111595</v>
+        <v>181138</v>
       </c>
       <c r="G26" s="18">
-        <v>620.19000000000005</v>
+        <v>2489.56</v>
       </c>
       <c r="H26" s="19">
-        <v>5.0308730656000002E-3</v>
+        <v>1.8153288266299999E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1776,25 +1835,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="F27" s="17">
-        <v>39000</v>
+        <v>244507</v>
       </c>
       <c r="G27" s="18">
-        <v>610.82000000000005</v>
+        <v>2070.61</v>
       </c>
       <c r="H27" s="19">
-        <v>4.9548652605000002E-3</v>
+        <v>1.5098403017799999E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1814,16 +1873,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="F28" s="17">
-        <v>98000</v>
+        <v>417500</v>
       </c>
       <c r="G28" s="18">
-        <v>603.67999999999995</v>
+        <v>2016.32</v>
       </c>
       <c r="H28" s="19">
-        <v>4.8969468263999998E-3</v>
+        <v>1.4702533056900001E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1834,25 +1893,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F29" s="17">
-        <v>107500</v>
+        <v>91633</v>
       </c>
       <c r="G29" s="18">
-        <v>569.59</v>
+        <v>1847.69</v>
       </c>
       <c r="H29" s="19">
-        <v>4.6204146945999997E-3</v>
+        <v>1.34729226035E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -1872,16 +1931,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F30" s="17">
-        <v>22600</v>
+        <v>31808</v>
       </c>
       <c r="G30" s="18">
-        <v>555.49</v>
+        <v>1696.48</v>
       </c>
       <c r="H30" s="19">
-        <v>4.5060379548000004E-3</v>
+        <v>1.23703347089E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -1901,16 +1960,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F31" s="17">
-        <v>1512</v>
+        <v>235209</v>
       </c>
       <c r="G31" s="18">
-        <v>420.27</v>
+        <v>1450.3</v>
       </c>
       <c r="H31" s="19">
-        <v>3.4091569088000001E-3</v>
+        <v>1.05752478239E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -1930,16 +1989,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F32" s="17">
-        <v>47200</v>
+        <v>11990</v>
       </c>
       <c r="G32" s="18">
-        <v>388.13</v>
+        <v>1344.08</v>
       </c>
       <c r="H32" s="19">
-        <v>3.1484428367999999E-3</v>
+        <v>9.8007164690999994E-3</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -1950,25 +2009,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>40</v>
-      </c>
       <c r="F33" s="17">
-        <v>6410</v>
+        <v>618534</v>
       </c>
       <c r="G33" s="18">
-        <v>309.91000000000003</v>
+        <v>1236.6400000000001</v>
       </c>
       <c r="H33" s="19">
-        <v>2.5139358451000001E-3</v>
+        <v>9.0172891602000003E-3</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -1988,16 +2047,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F34" s="17">
-        <v>2298</v>
+        <v>189310</v>
       </c>
       <c r="G34" s="18">
-        <v>263.98</v>
+        <v>1047.83</v>
       </c>
       <c r="H34" s="19">
-        <v>2.1413596992000002E-3</v>
+        <v>7.6405308744999997E-3</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2020,13 +2079,13 @@
         <v>83</v>
       </c>
       <c r="F35" s="17">
-        <v>98887</v>
+        <v>250000</v>
       </c>
       <c r="G35" s="18">
-        <v>202.8</v>
+        <v>882.25</v>
       </c>
       <c r="H35" s="19">
-        <v>1.6450782142000001E-3</v>
+        <v>6.4331603066E-3</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2046,16 +2105,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F36" s="17">
-        <v>15977</v>
+        <v>133166</v>
       </c>
       <c r="G36" s="18">
-        <v>186.53</v>
+        <v>777.96</v>
       </c>
       <c r="H36" s="19">
-        <v>1.5130988130999999E-3</v>
+        <v>5.6727020596000002E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2066,6 +2125,27 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="17">
+        <v>99400</v>
+      </c>
+      <c r="G37" s="18">
+        <v>712.15</v>
+      </c>
+      <c r="H37" s="19">
+        <v>5.1928309576E-3</v>
+      </c>
+      <c r="I37" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="14" t="s">
@@ -2073,28 +2153,28 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" s="12" t="s">
+      <c r="B38" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="17">
+        <v>175341</v>
+      </c>
+      <c r="G38" s="18">
+        <v>688.74</v>
+      </c>
+      <c r="H38" s="19">
+        <v>5.0221307221000001E-3</v>
+      </c>
+      <c r="I38" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="14" t="s">
@@ -2103,6 +2183,27 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="17">
+        <v>98000</v>
+      </c>
+      <c r="G39" s="18">
+        <v>649.15</v>
+      </c>
+      <c r="H39" s="19">
+        <v>4.7334497171999997E-3</v>
+      </c>
+      <c r="I39" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="14" t="s">
@@ -2110,28 +2211,28 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I40" s="12" t="s">
+      <c r="B40" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="17">
+        <v>8011</v>
+      </c>
+      <c r="G40" s="18">
+        <v>454.89</v>
+      </c>
+      <c r="H40" s="19">
+        <v>3.3169513083999998E-3</v>
+      </c>
+      <c r="I40" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="14" t="s">
@@ -2140,6 +2241,27 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="17">
+        <v>45000</v>
+      </c>
+      <c r="G41" s="18">
+        <v>323.77999999999997</v>
+      </c>
+      <c r="H41" s="19">
+        <v>2.3609279048000002E-3</v>
+      </c>
+      <c r="I41" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="14" t="s">
@@ -2147,28 +2269,26 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I42" s="12" t="s">
+      <c r="B42" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="17">
+        <v>-121125</v>
+      </c>
+      <c r="G42" s="18">
+        <v>-39.119999999999997</v>
+      </c>
+      <c r="H42" s="19">
+        <v>-2.8525387490000001E-4</v>
+      </c>
+      <c r="I42" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="14" t="s">
@@ -2185,7 +2305,7 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="10" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>13</v>
@@ -2200,10 +2320,10 @@
         <v>13</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>13</v>
@@ -2222,7 +2342,7 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="10" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>13</v>
@@ -2237,10 +2357,10 @@
         <v>13</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>13</v>
@@ -2259,7 +2379,7 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="10" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>13</v>
@@ -2274,10 +2394,10 @@
         <v>13</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>13</v>
@@ -2296,7 +2416,7 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>13</v>
@@ -2311,10 +2431,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>13</v>
@@ -2333,7 +2453,7 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="10" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>13</v>
@@ -2348,10 +2468,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>13</v>
@@ -2370,7 +2490,7 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="10" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>13</v>
@@ -2385,10 +2505,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>13</v>
@@ -2407,7 +2527,7 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>13</v>
@@ -2422,10 +2542,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>13</v>
@@ -2444,7 +2564,7 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>13</v>
@@ -2458,11 +2578,11 @@
       <c r="F58" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>87</v>
+      <c r="G58" s="12">
+        <v>2086.2200000000003</v>
+      </c>
+      <c r="H58" s="13">
+        <v>1.5212227480700001E-2</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>13</v>
@@ -2481,7 +2601,7 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>13</v>
@@ -2496,10 +2616,10 @@
         <v>13</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>13</v>
@@ -2518,7 +2638,7 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="10" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>13</v>
@@ -2533,10 +2653,10 @@
         <v>13</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>13</v>
@@ -2555,7 +2675,7 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>13</v>
@@ -2570,10 +2690,10 @@
         <v>13</v>
       </c>
       <c r="G64" s="12">
-        <v>87420.03</v>
+        <v>2086.2200000000003</v>
       </c>
       <c r="H64" s="13">
-        <v>0.70913602980790003</v>
+        <v>1.5212227480700001E-2</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>13</v>
@@ -2584,36 +2704,57 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="15" t="s">
-        <v>13</v>
+        <v>109</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F65" s="17">
+        <v>1200000</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1192.68</v>
+      </c>
+      <c r="H65" s="19">
+        <v>8.6967431391000004E-3</v>
+      </c>
+      <c r="I65" s="18">
+        <v>5.6</v>
       </c>
       <c r="J65" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="12">
-        <v>5000</v>
-      </c>
-      <c r="H66" s="13">
-        <v>4.0559127571100001E-2</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>13</v>
+      <c r="B66" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F66" s="17">
+        <v>900000</v>
+      </c>
+      <c r="G66" s="18">
+        <v>893.54</v>
+      </c>
+      <c r="H66" s="19">
+        <v>6.5154843416000002E-3</v>
+      </c>
+      <c r="I66" s="18">
+        <v>5.61</v>
       </c>
       <c r="J66" s="14" t="s">
         <v>13</v>
@@ -2621,20 +2762,6 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="G67" s="18">
-        <v>5000</v>
-      </c>
-      <c r="H67" s="19">
-        <v>4.0559127571100001E-2</v>
-      </c>
-      <c r="I67" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J67" s="14" t="s">
@@ -2642,7 +2769,28 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I68" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J68" s="14" t="s">
@@ -2650,149 +2798,411 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="21">
-        <v>-9384.2366308199853</v>
-      </c>
-      <c r="H69" s="22">
-        <v>-7.6123290133374794E-2</v>
-      </c>
-      <c r="I69" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="23" t="s">
+      <c r="B69" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="21">
-        <v>123276.81336918</v>
-      </c>
-      <c r="H70" s="22">
-        <v>0.99999999999842526</v>
-      </c>
-      <c r="I70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="23" t="s">
+      <c r="B70" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="12">
+        <v>15659.47</v>
+      </c>
+      <c r="H72" s="13">
+        <v>0.1141851865423</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
+      <c r="B73" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-    </row>
-    <row r="77" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-    </row>
-    <row r="80" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B80" s="24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B95" s="24" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="25" t="s">
-        <v>111</v>
+      <c r="B74" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="12">
+        <v>3000</v>
+      </c>
+      <c r="H74" s="13">
+        <v>2.1875297160500001E-2</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="G75" s="18">
+        <v>3000</v>
+      </c>
+      <c r="H75" s="19">
+        <v>2.1875297160500001E-2</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="21">
+        <v>229.78415331995348</v>
+      </c>
+      <c r="H77" s="22">
+        <v>1.6755322122213936E-3</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="21">
+        <v>137140.99415332</v>
+      </c>
+      <c r="H78" s="22">
+        <v>0.99999999999802147</v>
+      </c>
+      <c r="I78" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="17">
+        <v>-892125</v>
+      </c>
+      <c r="G83" s="18">
+        <v>-2242.89</v>
+      </c>
+      <c r="H83" s="19">
+        <v>-1.6354628416100001E-2</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+    </row>
+    <row r="99" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B99" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B114" s="24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="24" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B77:H77"/>
+  <mergeCells count="10">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="B91:I91"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B96:H96"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>